--- a/LISTAS_ORDENADAS/MI/Tenders Bnaqueta Barral/TENDEDERO RODANTE LISDISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tenders Bnaqueta Barral/TENDEDERO RODANTE LISDISMAY.xlsx
@@ -768,13 +768,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45202.60853093035</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -817,35 +813,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="19.5" customHeight="1" s="15">
       <c r="A41" s="4" t="n"/>
     </row>
@@ -879,10 +846,8 @@
         </is>
       </c>
       <c r="C43" s="13" t="n"/>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>**********</t>
-        </is>
+      <c r="D43" s="6" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="15">
@@ -901,7 +866,6 @@
         <v>17516.625</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -911,13 +875,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
